--- a/docs/redundancy_X.xlsx
+++ b/docs/redundancy_X.xlsx
@@ -504,12 +504,12 @@
           <t>Billings</t>
         </is>
       </c>
-      <c r="E3" s="2" t="n">
-        <v>120</v>
+      <c r="E3" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>d10 Fri 06:35 Jefferson Lines: Sheridan WY Taco Bell 1655 Coffeen Ave (Jefferson) -&gt; Vivian</t>
+          <t>first bus: start the next day instead; the clock starts at the first bus. Fri Nov 13 22:20 start gives 231.7 h (out/omni/x_fri.log)</t>
         </is>
       </c>
     </row>
@@ -533,11 +533,11 @@
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>120</v>
+        <v>24</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>d10 Fri 11:30 Jefferson Lines: Billings -&gt; Whitefish</t>
+          <t>Billings -&gt; Spokane is daily: next day's bus, same route, +24 h (Fri start runs the same shape, out/omni/x_fri.log)</t>
         </is>
       </c>
     </row>
